--- a/branches/feat/jardin-datenpunkte/observations-summary.xlsx
+++ b/branches/feat/jardin-datenpunkte/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="68">
   <si>
     <t>Profile</t>
   </si>
@@ -159,6 +159,33 @@
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-icf (required)</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#extent-of-impairment</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#extent-of-impairment-structure</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#nature-of-change</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#anatomical-location</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#capacity</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#performance</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#barrier</t>
+  </si>
+  <si>
+    <t>MII CS SE ICF Qualifier Kind#facilitator</t>
   </si>
   <si>
     <t>mii-pr-seltene-kopfumfang</t>
@@ -322,7 +349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -663,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>19</v>
@@ -677,34 +704,34 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="F11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>54</v>
-      </c>
       <c r="I11" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s" s="2">
         <v>14</v>
@@ -712,36 +739,316 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="F17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="F18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s" s="2">
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="H12" t="s" s="2">
+      <c r="H20" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s" s="2">
+      <c r="I20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/branches/feat/jardin-datenpunkte/observations-summary.xlsx
+++ b/branches/feat/jardin-datenpunkte/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="65">
   <si>
     <t>Profile</t>
   </si>
@@ -120,15 +120,6 @@
   </si>
   <si>
     <t>LOINC#89269-5</t>
-  </si>
-  <si>
-    <t>mii-pr-seltene-geschlecht-bei-geburt</t>
-  </si>
-  <si>
-    <t>MII PR SE Geschlecht bei Geburt</t>
-  </si>
-  <si>
-    <t>LOINC#76689-9</t>
   </si>
   <si>
     <t>mii-pr-seltene-gestationsalter</t>
@@ -349,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -570,7 +561,7 @@
         <v>37</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
@@ -585,7 +576,7 @@
         <v>24</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>19</v>
@@ -605,7 +596,7 @@
         <v>40</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>14</v>
@@ -640,22 +631,22 @@
         <v>43</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>19</v>
@@ -669,28 +660,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="F10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>19</v>
@@ -707,7 +698,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -716,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>14</v>
@@ -725,7 +716,7 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>19</v>
@@ -742,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -751,7 +742,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>14</v>
@@ -760,7 +751,7 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>19</v>
@@ -777,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>14</v>
@@ -786,7 +777,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>14</v>
@@ -795,7 +786,7 @@
         <v>14</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>19</v>
@@ -812,7 +803,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>14</v>
@@ -821,7 +812,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>14</v>
@@ -830,7 +821,7 @@
         <v>14</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -847,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -856,7 +847,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>14</v>
@@ -865,7 +856,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -882,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -891,7 +882,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -900,7 +891,7 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -917,7 +908,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -926,7 +917,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>14</v>
@@ -935,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>19</v>
@@ -949,34 +940,34 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>14</v>
@@ -984,71 +975,36 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s" s="2">
         <v>14</v>
       </c>
     </row>
